--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1027,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R5" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,23 +1092,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1146,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1148,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R6" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1218,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327955</v>
+        <v>131327964</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503765</v>
+        <v>503463</v>
       </c>
       <c r="R9" t="n">
-        <v>7021922</v>
+        <v>7021900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131327964</v>
+        <v>131327955</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503463</v>
+        <v>503765</v>
       </c>
       <c r="R11" t="n">
-        <v>7021900</v>
+        <v>7021922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R14" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R15" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327954</v>
+        <v>131327972</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503769</v>
+        <v>503450</v>
       </c>
       <c r="R18" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327972</v>
+        <v>131327954</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503450</v>
+        <v>503769</v>
       </c>
       <c r="R19" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131327961</v>
+        <v>131327966</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -3102,7 +3102,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503469</v>
+        <v>503457</v>
       </c>
       <c r="R21" t="n">
-        <v>7021944</v>
+        <v>7021904</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131327966</v>
+        <v>131327961</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3232,7 +3232,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503457</v>
+        <v>503469</v>
       </c>
       <c r="R22" t="n">
-        <v>7021904</v>
+        <v>7021944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327956</v>
+        <v>131327963</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503578</v>
+        <v>503470</v>
       </c>
       <c r="R26" t="n">
-        <v>7021915</v>
+        <v>7021909</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327963</v>
+        <v>131327956</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503470</v>
+        <v>503578</v>
       </c>
       <c r="R27" t="n">
-        <v>7021909</v>
+        <v>7021915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4108,7 +4108,7 @@
         <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327964</v>
+        <v>131327974</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503463</v>
+        <v>503445</v>
       </c>
       <c r="R9" t="n">
-        <v>7021900</v>
+        <v>7021903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327974</v>
+        <v>131327964</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503445</v>
+        <v>503463</v>
       </c>
       <c r="R10" t="n">
-        <v>7021903</v>
+        <v>7021900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R14" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R15" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327972</v>
+        <v>131327954</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503450</v>
+        <v>503769</v>
       </c>
       <c r="R18" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327954</v>
+        <v>131327965</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503769</v>
+        <v>503454</v>
       </c>
       <c r="R19" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131327965</v>
+        <v>131327972</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503454</v>
+        <v>503450</v>
       </c>
       <c r="R20" t="n">
         <v>7021902</v>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327963</v>
+        <v>131327960</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503470</v>
+        <v>503508</v>
       </c>
       <c r="R26" t="n">
-        <v>7021909</v>
+        <v>7021956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327956</v>
+        <v>131327963</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503578</v>
+        <v>503470</v>
       </c>
       <c r="R27" t="n">
-        <v>7021915</v>
+        <v>7021909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,10 +3975,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327960</v>
+        <v>131327956</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503508</v>
+        <v>503578</v>
       </c>
       <c r="R28" t="n">
-        <v>7021956</v>
+        <v>7021915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>83228</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,26 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R5" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1097,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>83229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,31 +1157,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R6" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,23 +1222,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92538</v>
+        <v>92539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327974</v>
+        <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503445</v>
+        <v>503463</v>
       </c>
       <c r="R9" t="n">
-        <v>7021903</v>
+        <v>7021900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327964</v>
+        <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503463</v>
+        <v>503445</v>
       </c>
       <c r="R10" t="n">
-        <v>7021900</v>
+        <v>7021903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R14" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R15" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327954</v>
+        <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503769</v>
+        <v>503450</v>
       </c>
       <c r="R18" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327965</v>
+        <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503454</v>
+        <v>503769</v>
       </c>
       <c r="R19" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131327972</v>
+        <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503450</v>
+        <v>503454</v>
       </c>
       <c r="R20" t="n">
         <v>7021902</v>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327960</v>
+        <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503508</v>
+        <v>503470</v>
       </c>
       <c r="R26" t="n">
-        <v>7021956</v>
+        <v>7021909</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327963</v>
+        <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503470</v>
+        <v>503578</v>
       </c>
       <c r="R27" t="n">
-        <v>7021909</v>
+        <v>7021915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,10 +3975,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327956</v>
+        <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503578</v>
+        <v>503508</v>
       </c>
       <c r="R28" t="n">
-        <v>7021915</v>
+        <v>7021956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,31 +4116,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,38 +4181,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4235,10 +4211,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,26 +4222,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4273,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R30" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,19 +4292,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>83229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1027,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R5" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,23 +1092,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1146,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>83229</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1148,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R6" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1218,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2159,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B14" t="n">
         <v>57887</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R14" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B15" t="n">
         <v>57887</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R15" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131327970</v>
+        <v>131327957</v>
       </c>
       <c r="B16" t="n">
         <v>57887</v>
@@ -2452,7 +2452,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503445</v>
+        <v>503562</v>
       </c>
       <c r="R16" t="n">
-        <v>7021905</v>
+        <v>7021924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131327957</v>
+        <v>131327970</v>
       </c>
       <c r="B17" t="n">
         <v>57887</v>
@@ -2582,7 +2582,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503562</v>
+        <v>503445</v>
       </c>
       <c r="R17" t="n">
-        <v>7021924</v>
+        <v>7021905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131327966</v>
+        <v>131327961</v>
       </c>
       <c r="B21" t="n">
         <v>57887</v>
@@ -3102,7 +3102,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503457</v>
+        <v>503469</v>
       </c>
       <c r="R21" t="n">
-        <v>7021904</v>
+        <v>7021944</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131327961</v>
+        <v>131327966</v>
       </c>
       <c r="B22" t="n">
         <v>57887</v>
@@ -3232,7 +3232,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503469</v>
+        <v>503457</v>
       </c>
       <c r="R22" t="n">
-        <v>7021944</v>
+        <v>7021904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327963</v>
+        <v>131327956</v>
       </c>
       <c r="B26" t="n">
         <v>57887</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503470</v>
+        <v>503578</v>
       </c>
       <c r="R26" t="n">
-        <v>7021909</v>
+        <v>7021915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327956</v>
+        <v>131327960</v>
       </c>
       <c r="B27" t="n">
         <v>57887</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503578</v>
+        <v>503508</v>
       </c>
       <c r="R27" t="n">
-        <v>7021915</v>
+        <v>7021956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327960</v>
+        <v>131327963</v>
       </c>
       <c r="B28" t="n">
         <v>57887</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503508</v>
+        <v>503470</v>
       </c>
       <c r="R28" t="n">
-        <v>7021956</v>
+        <v>7021909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -2159,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B14" t="n">
         <v>57887</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R14" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B15" t="n">
         <v>57887</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R15" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131327957</v>
+        <v>131327970</v>
       </c>
       <c r="B16" t="n">
         <v>57887</v>
@@ -2452,7 +2452,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503562</v>
+        <v>503445</v>
       </c>
       <c r="R16" t="n">
-        <v>7021924</v>
+        <v>7021905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131327970</v>
+        <v>131327957</v>
       </c>
       <c r="B17" t="n">
         <v>57887</v>
@@ -2582,7 +2582,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503445</v>
+        <v>503562</v>
       </c>
       <c r="R17" t="n">
-        <v>7021905</v>
+        <v>7021924</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3069,7 +3069,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131327961</v>
+        <v>131327966</v>
       </c>
       <c r="B21" t="n">
         <v>57887</v>
@@ -3102,7 +3102,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503469</v>
+        <v>503457</v>
       </c>
       <c r="R21" t="n">
-        <v>7021944</v>
+        <v>7021904</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131327966</v>
+        <v>131327961</v>
       </c>
       <c r="B22" t="n">
         <v>57887</v>
@@ -3232,7 +3232,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503457</v>
+        <v>503469</v>
       </c>
       <c r="R22" t="n">
-        <v>7021904</v>
+        <v>7021944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327956</v>
+        <v>131327963</v>
       </c>
       <c r="B26" t="n">
         <v>57887</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503578</v>
+        <v>503470</v>
       </c>
       <c r="R26" t="n">
-        <v>7021915</v>
+        <v>7021909</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327960</v>
+        <v>131327956</v>
       </c>
       <c r="B27" t="n">
         <v>57887</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503508</v>
+        <v>503578</v>
       </c>
       <c r="R27" t="n">
-        <v>7021956</v>
+        <v>7021915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327963</v>
+        <v>131327960</v>
       </c>
       <c r="B28" t="n">
         <v>57887</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503470</v>
+        <v>503508</v>
       </c>
       <c r="R28" t="n">
-        <v>7021909</v>
+        <v>7021956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>83229</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,26 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R5" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1097,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>83230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,31 +1157,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R6" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,23 +1222,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92539</v>
+        <v>92540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,31 +4116,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,38 +4181,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4235,10 +4211,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,26 +4222,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4273,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R30" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,19 +4292,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327964</v>
+        <v>131327974</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503463</v>
+        <v>503445</v>
       </c>
       <c r="R9" t="n">
-        <v>7021900</v>
+        <v>7021903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327974</v>
+        <v>131327964</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503445</v>
+        <v>503463</v>
       </c>
       <c r="R10" t="n">
-        <v>7021903</v>
+        <v>7021900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R14" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R15" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327972</v>
+        <v>131327954</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503450</v>
+        <v>503769</v>
       </c>
       <c r="R18" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327954</v>
+        <v>131327972</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503769</v>
+        <v>503450</v>
       </c>
       <c r="R19" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>80358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,31 +4116,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,38 +4181,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4235,10 +4211,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,26 +4222,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4273,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R30" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,19 +4292,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>83234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1027,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R5" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,23 +1092,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1146,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>83233</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1148,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R6" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1218,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327974</v>
+        <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503445</v>
+        <v>503463</v>
       </c>
       <c r="R9" t="n">
-        <v>7021903</v>
+        <v>7021900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327964</v>
+        <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503463</v>
+        <v>503445</v>
       </c>
       <c r="R10" t="n">
-        <v>7021900</v>
+        <v>7021903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R14" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R15" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327954</v>
+        <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503769</v>
+        <v>503450</v>
       </c>
       <c r="R18" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327972</v>
+        <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503450</v>
+        <v>503769</v>
       </c>
       <c r="R19" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58051</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,26 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R5" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1097,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,31 +1157,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R6" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,23 +1222,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1027,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R5" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,23 +1092,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1146,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1148,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R6" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1218,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2159,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B14" t="n">
         <v>57898</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R14" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R15" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327963</v>
+        <v>131327956</v>
       </c>
       <c r="B26" t="n">
         <v>57898</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503470</v>
+        <v>503578</v>
       </c>
       <c r="R26" t="n">
-        <v>7021909</v>
+        <v>7021915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327956</v>
+        <v>131327960</v>
       </c>
       <c r="B27" t="n">
         <v>57898</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503578</v>
+        <v>503508</v>
       </c>
       <c r="R27" t="n">
-        <v>7021915</v>
+        <v>7021956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327960</v>
+        <v>131327963</v>
       </c>
       <c r="B28" t="n">
         <v>57898</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503508</v>
+        <v>503470</v>
       </c>
       <c r="R28" t="n">
-        <v>7021956</v>
+        <v>7021909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,26 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R5" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1097,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,31 +1157,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R6" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,23 +1222,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327969</v>
+        <v>131327959</v>
       </c>
       <c r="B14" t="n">
         <v>57898</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503429</v>
+        <v>503527</v>
       </c>
       <c r="R14" t="n">
-        <v>7021902</v>
+        <v>7021942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327959</v>
+        <v>131327969</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503527</v>
+        <v>503429</v>
       </c>
       <c r="R15" t="n">
-        <v>7021942</v>
+        <v>7021902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327956</v>
+        <v>131327963</v>
       </c>
       <c r="B26" t="n">
         <v>57898</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503578</v>
+        <v>503470</v>
       </c>
       <c r="R26" t="n">
-        <v>7021915</v>
+        <v>7021909</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327960</v>
+        <v>131327956</v>
       </c>
       <c r="B27" t="n">
         <v>57898</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503508</v>
+        <v>503578</v>
       </c>
       <c r="R27" t="n">
-        <v>7021956</v>
+        <v>7021915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327963</v>
+        <v>131327960</v>
       </c>
       <c r="B28" t="n">
         <v>57898</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503470</v>
+        <v>503508</v>
       </c>
       <c r="R28" t="n">
-        <v>7021909</v>
+        <v>7021956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>131327967</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,31 +4116,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,38 +4181,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4235,10 +4211,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,26 +4222,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4273,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R30" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,19 +4292,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>83244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1027,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R5" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,23 +1092,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1146,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327952</v>
+        <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>83241</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1148,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503498</v>
+        <v>503419</v>
       </c>
       <c r="R6" t="n">
-        <v>7021967</v>
+        <v>7021902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1218,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>131327972</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131327954</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>131327965</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>58061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327964</v>
+        <v>131327955</v>
       </c>
       <c r="B9" t="n">
         <v>57902</v>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503463</v>
+        <v>503765</v>
       </c>
       <c r="R9" t="n">
-        <v>7021900</v>
+        <v>7021922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327974</v>
+        <v>131327968</v>
       </c>
       <c r="B10" t="n">
         <v>57902</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503445</v>
+        <v>503422</v>
       </c>
       <c r="R10" t="n">
-        <v>7021903</v>
+        <v>7021909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131327955</v>
+        <v>131327974</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1802,7 +1802,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503765</v>
+        <v>503445</v>
       </c>
       <c r="R11" t="n">
-        <v>7021922</v>
+        <v>7021903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131327968</v>
+        <v>131327964</v>
       </c>
       <c r="B12" t="n">
         <v>57902</v>
@@ -1932,7 +1932,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503422</v>
+        <v>503463</v>
       </c>
       <c r="R12" t="n">
-        <v>7021909</v>
+        <v>7021900</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2419,7 +2419,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131327970</v>
+        <v>131327957</v>
       </c>
       <c r="B16" t="n">
         <v>57902</v>
@@ -2452,7 +2452,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503445</v>
+        <v>503562</v>
       </c>
       <c r="R16" t="n">
-        <v>7021905</v>
+        <v>7021924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131327957</v>
+        <v>131327970</v>
       </c>
       <c r="B17" t="n">
         <v>57902</v>
@@ -2582,7 +2582,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503562</v>
+        <v>503445</v>
       </c>
       <c r="R17" t="n">
-        <v>7021924</v>
+        <v>7021905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,50 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +909,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,28 +993,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327955</v>
+        <v>131327964</v>
       </c>
       <c r="B9" t="n">
         <v>57902</v>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503765</v>
+        <v>503463</v>
       </c>
       <c r="R9" t="n">
-        <v>7021922</v>
+        <v>7021900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327968</v>
+        <v>131327974</v>
       </c>
       <c r="B10" t="n">
         <v>57902</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503422</v>
+        <v>503445</v>
       </c>
       <c r="R10" t="n">
-        <v>7021909</v>
+        <v>7021903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131327974</v>
+        <v>131327955</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1802,7 +1802,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503445</v>
+        <v>503765</v>
       </c>
       <c r="R11" t="n">
-        <v>7021903</v>
+        <v>7021922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131327964</v>
+        <v>131327968</v>
       </c>
       <c r="B12" t="n">
         <v>57902</v>
@@ -1932,7 +1932,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503463</v>
+        <v>503422</v>
       </c>
       <c r="R12" t="n">
-        <v>7021900</v>
+        <v>7021909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2419,7 +2419,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131327957</v>
+        <v>131327970</v>
       </c>
       <c r="B16" t="n">
         <v>57902</v>
@@ -2452,7 +2452,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503562</v>
+        <v>503445</v>
       </c>
       <c r="R16" t="n">
-        <v>7021924</v>
+        <v>7021905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,7 +2549,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131327970</v>
+        <v>131327957</v>
       </c>
       <c r="B17" t="n">
         <v>57902</v>
@@ -2582,7 +2582,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503445</v>
+        <v>503562</v>
       </c>
       <c r="R17" t="n">
-        <v>7021905</v>
+        <v>7021924</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,31 +4116,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,38 +4181,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4235,10 +4211,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B30" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,26 +4222,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4273,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R30" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,19 +4292,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327979</v>
+        <v>131327975</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503460</v>
+        <v>503459</v>
       </c>
       <c r="R3" t="n">
-        <v>7021909</v>
+        <v>7021911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,28 +872,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327975</v>
+        <v>131327979</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,50 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503459</v>
+        <v>503460</v>
       </c>
       <c r="R4" t="n">
-        <v>7021911</v>
+        <v>7021909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +977,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>131327952</v>
       </c>
       <c r="B5" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>131327967</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131327953</v>
       </c>
       <c r="B7" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131327977</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>131327964</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>131327974</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>131327955</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>131327968</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>131327971</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131327959</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131327969</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131327970</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>131327957</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327972</v>
+        <v>131327954</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503450</v>
+        <v>503769</v>
       </c>
       <c r="R18" t="n">
-        <v>7021902</v>
+        <v>7021932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131327954</v>
+        <v>131327965</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503769</v>
+        <v>503454</v>
       </c>
       <c r="R19" t="n">
-        <v>7021932</v>
+        <v>7021902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131327965</v>
+        <v>131327972</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503454</v>
+        <v>503450</v>
       </c>
       <c r="R20" t="n">
         <v>7021902</v>
@@ -3072,7 +3072,7 @@
         <v>131327966</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>131327961</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>131327973</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>131327962</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>131327978</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>131327963</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>131327956</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>131327960</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327976</v>
+        <v>131327958</v>
       </c>
       <c r="B29" t="n">
-        <v>80369</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,26 +4116,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4143,10 +4148,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503581</v>
+        <v>503543</v>
       </c>
       <c r="R29" t="n">
-        <v>7021963</v>
+        <v>7021931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4181,19 +4186,38 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4211,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131327958</v>
+        <v>131327976</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4222,31 +4246,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503543</v>
+        <v>503581</v>
       </c>
       <c r="R30" t="n">
-        <v>7021931</v>
+        <v>7021963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4292,38 +4311,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327963</v>
+        <v>131327956</v>
       </c>
       <c r="B26" t="n">
         <v>57904</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503470</v>
+        <v>503578</v>
       </c>
       <c r="R26" t="n">
-        <v>7021909</v>
+        <v>7021915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327956</v>
+        <v>131327960</v>
       </c>
       <c r="B27" t="n">
         <v>57904</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503578</v>
+        <v>503508</v>
       </c>
       <c r="R27" t="n">
-        <v>7021915</v>
+        <v>7021956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327960</v>
+        <v>131327963</v>
       </c>
       <c r="B28" t="n">
         <v>57904</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503508</v>
+        <v>503470</v>
       </c>
       <c r="R28" t="n">
-        <v>7021956</v>
+        <v>7021909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -3715,7 +3715,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327956</v>
+        <v>131327963</v>
       </c>
       <c r="B26" t="n">
         <v>57904</v>
@@ -3748,7 +3748,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503578</v>
+        <v>503470</v>
       </c>
       <c r="R26" t="n">
-        <v>7021915</v>
+        <v>7021909</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327960</v>
+        <v>131327956</v>
       </c>
       <c r="B27" t="n">
         <v>57904</v>
@@ -3878,7 +3878,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503508</v>
+        <v>503578</v>
       </c>
       <c r="R27" t="n">
-        <v>7021956</v>
+        <v>7021915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327963</v>
+        <v>131327960</v>
       </c>
       <c r="B28" t="n">
         <v>57904</v>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503470</v>
+        <v>503508</v>
       </c>
       <c r="R28" t="n">
-        <v>7021909</v>
+        <v>7021956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>116444437</v>
       </c>
       <c r="B2" t="n">
-        <v>90884</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,18 +695,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken (Sandtjärnbäcken), Jmt</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -777,61 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131327975</v>
+        <v>131327953</v>
       </c>
       <c r="B3" t="n">
-        <v>58063</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503459</v>
+        <v>503716</v>
       </c>
       <c r="R3" t="n">
-        <v>7021911</v>
+        <v>7021947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +854,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,14 +893,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131327979</v>
+        <v>131327978</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503460</v>
+        <v>503499</v>
       </c>
       <c r="R4" t="n">
-        <v>7021909</v>
+        <v>7021949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +981,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1016,32 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131327952</v>
+        <v>131327979</v>
       </c>
       <c r="B5" t="n">
-        <v>83246</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503498</v>
+        <v>503460</v>
       </c>
       <c r="R5" t="n">
-        <v>7021967</v>
+        <v>7021909</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1102,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1137,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131327967</v>
+        <v>131327952</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,31 +1146,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503419</v>
+        <v>503498</v>
       </c>
       <c r="R6" t="n">
-        <v>7021902</v>
+        <v>7021967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,23 +1211,19 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1267,32 +1256,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131327953</v>
+        <v>131327976</v>
       </c>
       <c r="B7" t="n">
-        <v>92561</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503716</v>
+        <v>503581</v>
       </c>
       <c r="R7" t="n">
-        <v>7021947</v>
+        <v>7021963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,21 +1345,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1388,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131327977</v>
+        <v>131327954</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,24 +1373,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1426,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503769</v>
       </c>
       <c r="R8" t="n">
-        <v>7021934</v>
+        <v>7021932</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,19 +1443,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1509,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131327964</v>
+        <v>131327955</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503463</v>
+        <v>503765</v>
       </c>
       <c r="R9" t="n">
-        <v>7021900</v>
+        <v>7021922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131327974</v>
+        <v>131327956</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503445</v>
+        <v>503578</v>
       </c>
       <c r="R10" t="n">
-        <v>7021903</v>
+        <v>7021915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131327955</v>
+        <v>131327957</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1785,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1812,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503765</v>
+        <v>503562</v>
       </c>
       <c r="R11" t="n">
-        <v>7021922</v>
+        <v>7021924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1852,7 +1835,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131327968</v>
+        <v>131327958</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1915,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1942,10 +1925,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503422</v>
+        <v>503543</v>
       </c>
       <c r="R12" t="n">
-        <v>7021909</v>
+        <v>7021931</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1982,7 +1965,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2029,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131327971</v>
+        <v>131327959</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2045,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2072,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503437</v>
+        <v>503527</v>
       </c>
       <c r="R13" t="n">
-        <v>7021905</v>
+        <v>7021942</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2112,7 +2095,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,10 +2142,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131327959</v>
+        <v>131327960</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,10 +2185,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503527</v>
+        <v>503508</v>
       </c>
       <c r="R14" t="n">
-        <v>7021942</v>
+        <v>7021956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,10 +2272,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131327969</v>
+        <v>131327961</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,10 +2315,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503429</v>
+        <v>503469</v>
       </c>
       <c r="R15" t="n">
-        <v>7021902</v>
+        <v>7021944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131327970</v>
+        <v>131327962</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,10 +2445,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503445</v>
+        <v>503472</v>
       </c>
       <c r="R16" t="n">
-        <v>7021905</v>
+        <v>7021909</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2485,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,17 +2504,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2549,10 +2532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131327957</v>
+        <v>131327963</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2582,7 +2565,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2592,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503562</v>
+        <v>503470</v>
       </c>
       <c r="R17" t="n">
-        <v>7021924</v>
+        <v>7021909</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2632,7 +2615,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2679,10 +2662,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131327954</v>
+        <v>131327964</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,10 +2705,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503769</v>
+        <v>503463</v>
       </c>
       <c r="R18" t="n">
-        <v>7021932</v>
+        <v>7021900</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2812,7 +2795,7 @@
         <v>131327965</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2939,10 +2922,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131327972</v>
+        <v>131327966</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2972,7 +2955,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2982,10 +2965,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503450</v>
+        <v>503457</v>
       </c>
       <c r="R20" t="n">
-        <v>7021902</v>
+        <v>7021904</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3022,7 +3005,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3069,10 +3052,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131327966</v>
+        <v>131327967</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3112,10 +3095,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503457</v>
+        <v>503419</v>
       </c>
       <c r="R21" t="n">
-        <v>7021904</v>
+        <v>7021902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3199,10 +3182,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131327961</v>
+        <v>131327968</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3232,7 +3215,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3242,10 +3225,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503469</v>
+        <v>503422</v>
       </c>
       <c r="R22" t="n">
-        <v>7021944</v>
+        <v>7021909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3265,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3329,10 +3312,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131327973</v>
+        <v>131327969</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3345,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3372,10 +3355,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503440</v>
+        <v>503429</v>
       </c>
       <c r="R23" t="n">
-        <v>7021904</v>
+        <v>7021902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3412,7 +3395,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,14 +3422,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3464,10 +3442,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131327962</v>
+        <v>131327970</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3507,10 +3485,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503472</v>
+        <v>503445</v>
       </c>
       <c r="R24" t="n">
-        <v>7021909</v>
+        <v>7021905</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3547,7 +3525,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3566,17 +3544,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3594,10 +3572,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131327978</v>
+        <v>131327971</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,26 +3583,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3632,10 +3615,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503499</v>
+        <v>503437</v>
       </c>
       <c r="R25" t="n">
-        <v>7021949</v>
+        <v>7021905</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3670,19 +3653,23 @@
           <t>2026-01-25</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3715,10 +3702,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131327963</v>
+        <v>131327972</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3758,10 +3745,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503470</v>
+        <v>503450</v>
       </c>
       <c r="R26" t="n">
-        <v>7021909</v>
+        <v>7021902</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3845,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131327956</v>
+        <v>131327973</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3888,10 +3875,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503578</v>
+        <v>503440</v>
       </c>
       <c r="R27" t="n">
-        <v>7021915</v>
+        <v>7021904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3955,9 +3942,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3975,10 +3967,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131327960</v>
+        <v>131327974</v>
       </c>
       <c r="B28" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4008,7 +4000,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4018,10 +4010,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503508</v>
+        <v>503445</v>
       </c>
       <c r="R28" t="n">
-        <v>7021956</v>
+        <v>7021903</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4058,7 +4050,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4105,10 +4097,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131327958</v>
+        <v>131327975</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4116,42 +4108,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Eliasbodarna Väst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503543</v>
+        <v>503459</v>
       </c>
       <c r="R29" t="n">
-        <v>7021931</v>
+        <v>7021911</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4186,11 +4186,6 @@
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4203,21 +4198,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4232,112 +4212,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>131327976</v>
-      </c>
-      <c r="B30" t="n">
-        <v>80371</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Eliasbodarna Väst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>503581</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7021963</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3894-2026 artfynd.xlsx
+++ b/artfynd/A 3894-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116444437</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327978</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327952</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327976</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327954</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1619,6 +1659,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327955</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1749,6 +1794,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327956</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1879,6 +1929,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327957</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2009,6 +2064,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327958</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2139,6 +2199,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327959</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2269,6 +2334,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327960</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2399,6 +2469,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327961</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2529,6 +2604,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327962</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2659,6 +2739,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2789,6 +2874,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327964</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2919,6 +3009,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327965</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3049,6 +3144,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327966</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3179,6 +3279,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327967</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3309,6 +3414,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327968</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3439,6 +3549,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327969</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3569,6 +3684,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327970</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3699,6 +3819,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327971</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3829,6 +3954,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327972</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3964,6 +4094,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327973</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4094,6 +4229,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327974</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4212,8 +4352,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131327975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>